--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>41</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>246</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>231</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>126</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>309</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>248</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>383</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>372</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>287</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>428</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>443</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>276</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>275</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>236</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>218</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>240</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>221</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>331</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>247</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>222</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>112</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>222</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>111</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>336</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>138</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>289</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>116</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>248</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>112</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>222</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>337</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>112</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>339</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>210</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>134</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>114</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>344</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>228</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>18</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>117</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>116</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>230</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>347</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>230</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>257</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>42</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>138</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>245</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>230</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>345</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>290</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>115</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>271</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>248</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>223</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>330</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>220</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>288</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>110</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>339</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>204</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>112</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>112</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>336</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">

--- a/output/vuse-de.xlsx
+++ b/output/vuse-de.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>224</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>234</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
